--- a/Kafedra/КЗФ_Наукова_робота_Оліх.xlsx
+++ b/Kafedra/КЗФ_Наукова_робота_Оліх.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DeepL\Kafedra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{525E4993-1865-42FD-A000-0EA25FBE1B29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C63D45B-45D0-4403-B837-14EC3F669363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Аркуш1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2175,6 +2175,39 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2220,9 +2253,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2232,37 +2262,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2579,19 +2579,19 @@
       <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:22" s="3" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="91" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="97" t="s">
+      <c r="C2" s="79" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="97" t="s">
+      <c r="D2" s="79" t="s">
         <v>99</v>
       </c>
-      <c r="E2" s="84" t="s">
+      <c r="E2" s="95" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="48" t="s">
@@ -2620,11 +2620,11 @@
       </c>
     </row>
     <row r="3" spans="1:22" s="3" customFormat="1" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="81"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="98"/>
-      <c r="D3" s="98"/>
-      <c r="E3" s="85"/>
+      <c r="A3" s="92"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="96"/>
       <c r="F3" s="23">
         <f>F5*E5+F6*E6+F7*E7+F8*E8+F9*E9+F10*E10+F11*E11+F12*E12+F13*E13+F14*E14+F15*E15+F16*E16+F17*E17+F18*E18+F19*E19+F20*E20+F21*E21+F22*E22+F23*E23+F24*E24+F25*E25+F26*E26+F27*E27+F28*E28+F29*E29+F30*E30+F31*E31+F33*E33+F34*E34+F35*E35+F36*E36+F37*E37+F38*E38+F39*E39+F40*E40+F41*E41+F42*E42+F43*E43+F44*E44+F45*E45+F46*E46+F47*E47+F48*E48+F49*E49+F50*E50+F51*E51+F52*E52+F53*E53+F54*E54+F55*E55+F56*E56+F57*E57+F58*E58+F60*E60+F61*E61+F62*E62+F63*E63+F64*E64+F65*E65+F66*E66+F67*E67+F68*E68+F69*E69+F70*E70+F71*E71+F72*E72+F73*E73+F74*E74+F75*E75+F77*E77+F78*E78+F79*E79+F80*E80+F81*E81+F82*E82+F83*E83+F84*E84+F85*E85+F86*E86+F87*E87+F88*E88+F89*E89</f>
         <v>0</v>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="K3" s="25">
         <f>K5*$E5+K6*$E6+K7*$E7+K8*$E8+K9*$E9+K10*$E10+K11*$E11+K12*$E12+K13*$E13+K14*$E14+K15*$E15+K16*$E16+K17*$E17+K18*$E18+K19*$E19+K20*$E20+K21*$E21+K22*$E22+K23*$E23+K24*$E24+K25*$E25+K26*$E26+K27*$E27+K28*$E28+K29*$E29+K30*$E30+K31*$E31+K33*$E33+K34*$E34+K35*$E35+K36*$E36+K37*$E37+K38*$E38+K39*$E39+K40*$E40+K41*$E41+K42*$E42+K43*$E43+K44*$E44+K45*$E45+K46*$E46+K47*$E47+K48*$E48+K49*$E49+K50*$E50+K51*$E51+K52*$E52+K53*$E53+K54*$E54+K55*$E55+K56*$E56+K57*$E57+K58*$E58+K60*$E60+K61*$E61+K62*$E62+K63*$E63+K64*$E64+K65*$E65+K66*$E66+K67*$E67+K68*$E68+K69*$E69+K70*$E70+K71*$E71+K72*$E72+K73*$E73+K74*$E74+K75*$E75+K77*$E77+K78*$E78+K79*$E79+K80*$E80+K81*$E81+K82*$E82+K83*$E83+K84*$E84+K85*$E85+K86*$E86+K87*$E87+K88*$E88+K89*$E89</f>
-        <v>348</v>
+        <v>508</v>
       </c>
       <c r="L3" s="62">
         <f>L5*$E5+L6*$E6+L7*$E7+L8*$E8+L9*$E9+L10*$E10+L11*$E11+L12*$E12+L13*$E13+L14*$E14+L15*$E15+L16*$E16+L17*$E17+L18*$E18+L19*$E19+L20*$E20+L21*$E21+L22*$E22+L23*$E23+L24*$E24+L25*$E25+L26*$E26+L27*$E27+L28*$E28+L29*$E29+L30*$E30+L31*$E31+L33*$E33+L34*$E34+L35*$E35+L36*$E36+L37*$E37+L38*$E38+L39*$E39+L40*$E40+L41*$E41+L42*$E42+L43*$E43+L44*$E44+L45*$E45+L46*$E46+L47*$E47+L48*$E48+L49*$E49+L50*$E50+L51*$E51+L52*$E52+L53*$E53+L54*$E54+L55*$E55+L56*$E56+L57*$E57+L58*$E58+L60*$E60+L61*$E61+L62*$E62+L63*$E63+L64*$E64+L65*$E65+L66*$E66+L67*$E67+L68*$E68+L69*$E69+L70*$E70+L71*$E71+L72*$E72+L73*$E73+L74*$E74+L75*$E75+L77*$E77+L78*$E78+L79*$E79+L80*$E80+L81*$E81+L82*$E82+L83*$E83+L84*$E84+L85*$E85+L86*$E86+L87*$E87+L88*$E88+L89*$E89</f>
@@ -2659,21 +2659,21 @@
       </c>
     </row>
     <row r="4" spans="1:22" s="3" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="71" t="s">
+      <c r="A4" s="82" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="72"/>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="72"/>
-      <c r="L4" s="72"/>
-      <c r="M4" s="73"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="83"/>
+      <c r="K4" s="83"/>
+      <c r="L4" s="83"/>
+      <c r="M4" s="84"/>
       <c r="N4" s="60"/>
       <c r="O4" s="60"/>
       <c r="P4" s="60"/>
@@ -2691,10 +2691,10 @@
       <c r="B5" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="C5" s="92" t="s">
+      <c r="C5" s="100" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="89" t="s">
+      <c r="D5" s="99" t="s">
         <v>120</v>
       </c>
       <c r="E5" s="55">
@@ -2716,8 +2716,8 @@
       <c r="B6" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C6" s="93"/>
-      <c r="D6" s="90"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="75"/>
       <c r="E6" s="56">
         <v>100</v>
       </c>
@@ -2726,7 +2726,9 @@
       <c r="H6" s="34"/>
       <c r="I6" s="37"/>
       <c r="J6" s="40"/>
-      <c r="K6" s="43"/>
+      <c r="K6" s="43">
+        <v>1</v>
+      </c>
       <c r="L6" s="64"/>
       <c r="M6" s="69"/>
     </row>
@@ -2737,8 +2739,8 @@
       <c r="B7" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="94"/>
-      <c r="D7" s="90"/>
+      <c r="C7" s="72"/>
+      <c r="D7" s="75"/>
       <c r="E7" s="56">
         <v>100</v>
       </c>
@@ -2761,7 +2763,7 @@
       <c r="C8" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D8" s="91"/>
+      <c r="D8" s="76"/>
       <c r="E8" s="56">
         <v>75</v>
       </c>
@@ -2800,13 +2802,13 @@
       <c r="M9" s="69"/>
     </row>
     <row r="10" spans="1:22" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A10" s="86" t="s">
+      <c r="A10" s="77" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="99" t="s">
+      <c r="C10" s="81" t="s">
         <v>100</v>
       </c>
       <c r="D10" s="46" t="s">
@@ -2825,12 +2827,12 @@
       <c r="M10" s="69"/>
     </row>
     <row r="11" spans="1:22" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A11" s="86"/>
+      <c r="A11" s="77"/>
       <c r="B11" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="93"/>
-      <c r="D11" s="90" t="s">
+      <c r="C11" s="71"/>
+      <c r="D11" s="75" t="s">
         <v>131</v>
       </c>
       <c r="E11" s="57">
@@ -2846,12 +2848,12 @@
       <c r="M11" s="69"/>
     </row>
     <row r="12" spans="1:22" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A12" s="86"/>
+      <c r="A12" s="77"/>
       <c r="B12" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="93"/>
-      <c r="D12" s="90"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="75"/>
       <c r="E12" s="57">
         <v>200</v>
       </c>
@@ -2867,12 +2869,12 @@
       <c r="M12" s="69"/>
     </row>
     <row r="13" spans="1:22" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A13" s="86"/>
+      <c r="A13" s="77"/>
       <c r="B13" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="93"/>
-      <c r="D13" s="90"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="75"/>
       <c r="E13" s="57">
         <v>150</v>
       </c>
@@ -2886,12 +2888,12 @@
       <c r="M13" s="69"/>
     </row>
     <row r="14" spans="1:22" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A14" s="86"/>
+      <c r="A14" s="77"/>
       <c r="B14" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="93"/>
-      <c r="D14" s="90"/>
+      <c r="C14" s="71"/>
+      <c r="D14" s="75"/>
       <c r="E14" s="57">
         <v>125</v>
       </c>
@@ -2905,12 +2907,12 @@
       <c r="M14" s="69"/>
     </row>
     <row r="15" spans="1:22" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A15" s="86"/>
+      <c r="A15" s="77"/>
       <c r="B15" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="C15" s="93"/>
-      <c r="D15" s="90"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="75"/>
       <c r="E15" s="57">
         <v>100</v>
       </c>
@@ -2924,12 +2926,12 @@
       <c r="M15" s="69"/>
     </row>
     <row r="16" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="86"/>
+      <c r="A16" s="77"/>
       <c r="B16" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="94"/>
-      <c r="D16" s="91"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="76"/>
       <c r="E16" s="57">
         <v>100</v>
       </c>
@@ -2966,16 +2968,16 @@
       <c r="M17" s="69"/>
     </row>
     <row r="18" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A18" s="87" t="s">
+      <c r="A18" s="97" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C18" s="93" t="s">
+      <c r="C18" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="D18" s="95"/>
+      <c r="D18" s="78"/>
       <c r="E18" s="59">
         <v>150</v>
       </c>
@@ -2989,12 +2991,12 @@
       <c r="M18" s="69"/>
     </row>
     <row r="19" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A19" s="88"/>
+      <c r="A19" s="98"/>
       <c r="B19" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="94"/>
-      <c r="D19" s="96"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="74"/>
       <c r="E19" s="57">
         <v>100</v>
       </c>
@@ -3008,16 +3010,16 @@
       <c r="M19" s="69"/>
     </row>
     <row r="20" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A20" s="86" t="s">
+      <c r="A20" s="77" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="C20" s="93" t="s">
+      <c r="C20" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="D20" s="95"/>
+      <c r="D20" s="78"/>
       <c r="E20" s="59">
         <v>100</v>
       </c>
@@ -3031,12 +3033,12 @@
       <c r="M20" s="69"/>
     </row>
     <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A21" s="86"/>
+      <c r="A21" s="77"/>
       <c r="B21" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="94"/>
-      <c r="D21" s="96"/>
+      <c r="C21" s="72"/>
+      <c r="D21" s="74"/>
       <c r="E21" s="57">
         <v>50</v>
       </c>
@@ -3261,7 +3263,7 @@
       <c r="I30" s="37"/>
       <c r="J30" s="40"/>
       <c r="K30" s="43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L30" s="64"/>
       <c r="M30" s="69"/>
@@ -3290,21 +3292,21 @@
       <c r="M31" s="69"/>
     </row>
     <row r="32" spans="1:13" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="74" t="s">
+      <c r="A32" s="85" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="75"/>
-      <c r="C32" s="75"/>
-      <c r="D32" s="75"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
-      <c r="K32" s="75"/>
-      <c r="L32" s="75"/>
-      <c r="M32" s="76"/>
+      <c r="B32" s="86"/>
+      <c r="C32" s="86"/>
+      <c r="D32" s="86"/>
+      <c r="E32" s="86"/>
+      <c r="F32" s="86"/>
+      <c r="G32" s="86"/>
+      <c r="H32" s="86"/>
+      <c r="I32" s="86"/>
+      <c r="J32" s="86"/>
+      <c r="K32" s="86"/>
+      <c r="L32" s="86"/>
+      <c r="M32" s="87"/>
     </row>
     <row r="33" spans="1:13" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
@@ -3424,16 +3426,16 @@
       <c r="M37" s="69"/>
     </row>
     <row r="38" spans="1:13" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A38" s="86" t="s">
+      <c r="A38" s="77" t="s">
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C38" s="93" t="s">
+      <c r="C38" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="D38" s="90" t="s">
+      <c r="D38" s="75" t="s">
         <v>179</v>
       </c>
       <c r="E38" s="59">
@@ -3449,12 +3451,12 @@
       <c r="M38" s="69"/>
     </row>
     <row r="39" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A39" s="86"/>
+      <c r="A39" s="77"/>
       <c r="B39" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C39" s="93"/>
-      <c r="D39" s="90"/>
+      <c r="C39" s="71"/>
+      <c r="D39" s="75"/>
       <c r="E39" s="57">
         <v>50</v>
       </c>
@@ -3468,12 +3470,12 @@
       <c r="M39" s="69"/>
     </row>
     <row r="40" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A40" s="86"/>
+      <c r="A40" s="77"/>
       <c r="B40" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="93"/>
-      <c r="D40" s="90"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="75"/>
       <c r="E40" s="57">
         <v>100</v>
       </c>
@@ -3487,12 +3489,12 @@
       <c r="M40" s="69"/>
     </row>
     <row r="41" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A41" s="86"/>
+      <c r="A41" s="77"/>
       <c r="B41" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="93"/>
-      <c r="D41" s="90"/>
+      <c r="C41" s="71"/>
+      <c r="D41" s="75"/>
       <c r="E41" s="57">
         <v>75</v>
       </c>
@@ -3506,12 +3508,12 @@
       <c r="M41" s="69"/>
     </row>
     <row r="42" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A42" s="86"/>
+      <c r="A42" s="77"/>
       <c r="B42" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="93"/>
-      <c r="D42" s="90"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="75"/>
       <c r="E42" s="57">
         <v>100</v>
       </c>
@@ -3525,12 +3527,12 @@
       <c r="M42" s="69"/>
     </row>
     <row r="43" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A43" s="86"/>
+      <c r="A43" s="77"/>
       <c r="B43" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="93"/>
-      <c r="D43" s="90"/>
+      <c r="C43" s="71"/>
+      <c r="D43" s="75"/>
       <c r="E43" s="57">
         <v>75</v>
       </c>
@@ -3544,12 +3546,12 @@
       <c r="M43" s="69"/>
     </row>
     <row r="44" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A44" s="86"/>
+      <c r="A44" s="77"/>
       <c r="B44" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="94"/>
-      <c r="D44" s="90"/>
+      <c r="C44" s="72"/>
+      <c r="D44" s="75"/>
       <c r="E44" s="57">
         <v>50</v>
       </c>
@@ -3572,7 +3574,7 @@
       <c r="C45" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="D45" s="91"/>
+      <c r="D45" s="76"/>
       <c r="E45" s="57">
         <v>10</v>
       </c>
@@ -3636,16 +3638,16 @@
       <c r="M47" s="69"/>
     </row>
     <row r="48" spans="1:13" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A48" s="86" t="s">
+      <c r="A48" s="77" t="s">
         <v>40</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C48" s="93" t="s">
+      <c r="C48" s="71" t="s">
         <v>108</v>
       </c>
-      <c r="D48" s="90" t="s">
+      <c r="D48" s="75" t="s">
         <v>125</v>
       </c>
       <c r="E48" s="59">
@@ -3663,12 +3665,12 @@
       <c r="M48" s="69"/>
     </row>
     <row r="49" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A49" s="86"/>
+      <c r="A49" s="77"/>
       <c r="B49" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="94"/>
-      <c r="D49" s="91"/>
+      <c r="C49" s="72"/>
+      <c r="D49" s="76"/>
       <c r="E49" s="57">
         <v>30</v>
       </c>
@@ -3682,16 +3684,16 @@
       <c r="M49" s="69"/>
     </row>
     <row r="50" spans="1:13" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A50" s="86" t="s">
+      <c r="A50" s="77" t="s">
         <v>41</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C50" s="93" t="s">
+      <c r="C50" s="71" t="s">
         <v>103</v>
       </c>
-      <c r="D50" s="90" t="s">
+      <c r="D50" s="75" t="s">
         <v>125</v>
       </c>
       <c r="E50" s="59">
@@ -3707,12 +3709,12 @@
       <c r="M50" s="69"/>
     </row>
     <row r="51" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="86"/>
+      <c r="A51" s="77"/>
       <c r="B51" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C51" s="94"/>
-      <c r="D51" s="91"/>
+      <c r="C51" s="72"/>
+      <c r="D51" s="76"/>
       <c r="E51" s="57">
         <v>40</v>
       </c>
@@ -3726,16 +3728,16 @@
       <c r="M51" s="69"/>
     </row>
     <row r="52" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A52" s="86" t="s">
+      <c r="A52" s="77" t="s">
         <v>60</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C52" s="93" t="s">
+      <c r="C52" s="71" t="s">
         <v>134</v>
       </c>
-      <c r="D52" s="90" t="s">
+      <c r="D52" s="75" t="s">
         <v>180</v>
       </c>
       <c r="E52" s="59">
@@ -3751,12 +3753,12 @@
       <c r="M52" s="69"/>
     </row>
     <row r="53" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A53" s="86"/>
+      <c r="A53" s="77"/>
       <c r="B53" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="93"/>
-      <c r="D53" s="90"/>
+      <c r="C53" s="71"/>
+      <c r="D53" s="75"/>
       <c r="E53" s="57">
         <v>8</v>
       </c>
@@ -3770,12 +3772,12 @@
       <c r="M53" s="69"/>
     </row>
     <row r="54" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A54" s="86"/>
+      <c r="A54" s="77"/>
       <c r="B54" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C54" s="93"/>
-      <c r="D54" s="90"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="75"/>
       <c r="E54" s="57">
         <v>12</v>
       </c>
@@ -3789,12 +3791,12 @@
       <c r="M54" s="69"/>
     </row>
     <row r="55" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A55" s="86"/>
+      <c r="A55" s="77"/>
       <c r="B55" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C55" s="94"/>
-      <c r="D55" s="91"/>
+      <c r="C55" s="72"/>
+      <c r="D55" s="76"/>
       <c r="E55" s="57">
         <v>6</v>
       </c>
@@ -3881,21 +3883,21 @@
       <c r="M58" s="69"/>
     </row>
     <row r="59" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A59" s="74" t="s">
+      <c r="A59" s="85" t="s">
         <v>65</v>
       </c>
-      <c r="B59" s="75"/>
-      <c r="C59" s="75"/>
-      <c r="D59" s="75"/>
-      <c r="E59" s="75"/>
-      <c r="F59" s="75"/>
-      <c r="G59" s="75"/>
-      <c r="H59" s="75"/>
-      <c r="I59" s="75"/>
-      <c r="J59" s="75"/>
-      <c r="K59" s="75"/>
-      <c r="L59" s="75"/>
-      <c r="M59" s="76"/>
+      <c r="B59" s="86"/>
+      <c r="C59" s="86"/>
+      <c r="D59" s="86"/>
+      <c r="E59" s="86"/>
+      <c r="F59" s="86"/>
+      <c r="G59" s="86"/>
+      <c r="H59" s="86"/>
+      <c r="I59" s="86"/>
+      <c r="J59" s="86"/>
+      <c r="K59" s="86"/>
+      <c r="L59" s="86"/>
+      <c r="M59" s="87"/>
     </row>
     <row r="60" spans="1:13" ht="41.4" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
@@ -3923,16 +3925,16 @@
       <c r="M60" s="69"/>
     </row>
     <row r="61" spans="1:13" ht="69" x14ac:dyDescent="0.25">
-      <c r="A61" s="86" t="s">
+      <c r="A61" s="77" t="s">
         <v>68</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="C61" s="93" t="s">
+      <c r="C61" s="71" t="s">
         <v>101</v>
       </c>
-      <c r="D61" s="90" t="s">
+      <c r="D61" s="75" t="s">
         <v>127</v>
       </c>
       <c r="E61" s="59">
@@ -3948,12 +3950,12 @@
       <c r="M61" s="69"/>
     </row>
     <row r="62" spans="1:13" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A62" s="86"/>
+      <c r="A62" s="77"/>
       <c r="B62" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C62" s="94"/>
-      <c r="D62" s="91"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="76"/>
       <c r="E62" s="57">
         <v>5</v>
       </c>
@@ -3967,14 +3969,14 @@
       <c r="M62" s="69"/>
     </row>
     <row r="63" spans="1:13" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A63" s="86"/>
+      <c r="A63" s="77"/>
       <c r="B63" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="C63" s="93" t="s">
+      <c r="C63" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="D63" s="90" t="s">
+      <c r="D63" s="75" t="s">
         <v>132</v>
       </c>
       <c r="E63" s="59">
@@ -3990,12 +3992,12 @@
       <c r="M63" s="69"/>
     </row>
     <row r="64" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A64" s="86"/>
+      <c r="A64" s="77"/>
       <c r="B64" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C64" s="93"/>
-      <c r="D64" s="90"/>
+      <c r="C64" s="71"/>
+      <c r="D64" s="75"/>
       <c r="E64" s="57">
         <v>30</v>
       </c>
@@ -4009,12 +4011,12 @@
       <c r="M64" s="69"/>
     </row>
     <row r="65" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A65" s="86"/>
+      <c r="A65" s="77"/>
       <c r="B65" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C65" s="93"/>
-      <c r="D65" s="90"/>
+      <c r="C65" s="71"/>
+      <c r="D65" s="75"/>
       <c r="E65" s="57">
         <v>50</v>
       </c>
@@ -4028,12 +4030,12 @@
       <c r="M65" s="69"/>
     </row>
     <row r="66" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A66" s="86"/>
+      <c r="A66" s="77"/>
       <c r="B66" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C66" s="94"/>
-      <c r="D66" s="91"/>
+      <c r="C66" s="72"/>
+      <c r="D66" s="76"/>
       <c r="E66" s="57">
         <v>30</v>
       </c>
@@ -4118,16 +4120,16 @@
       <c r="M69" s="69"/>
     </row>
     <row r="70" spans="1:13" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A70" s="86" t="s">
+      <c r="A70" s="77" t="s">
         <v>76</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C70" s="93" t="s">
+      <c r="C70" s="71" t="s">
         <v>112</v>
       </c>
-      <c r="D70" s="95"/>
+      <c r="D70" s="78"/>
       <c r="E70" s="59">
         <v>2</v>
       </c>
@@ -4141,12 +4143,12 @@
       <c r="M70" s="69"/>
     </row>
     <row r="71" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A71" s="86"/>
+      <c r="A71" s="77"/>
       <c r="B71" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C71" s="94"/>
-      <c r="D71" s="96"/>
+      <c r="C71" s="72"/>
+      <c r="D71" s="74"/>
       <c r="E71" s="57">
         <v>4</v>
       </c>
@@ -4162,16 +4164,16 @@
       <c r="M71" s="69"/>
     </row>
     <row r="72" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A72" s="86" t="s">
+      <c r="A72" s="77" t="s">
         <v>77</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C72" s="93" t="s">
+      <c r="C72" s="71" t="s">
         <v>113</v>
       </c>
-      <c r="D72" s="95"/>
+      <c r="D72" s="78"/>
       <c r="E72" s="59">
         <v>2</v>
       </c>
@@ -4185,12 +4187,12 @@
       <c r="M72" s="69"/>
     </row>
     <row r="73" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A73" s="86"/>
+      <c r="A73" s="77"/>
       <c r="B73" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C73" s="94"/>
-      <c r="D73" s="96"/>
+      <c r="C73" s="72"/>
+      <c r="D73" s="74"/>
       <c r="E73" s="57">
         <v>4</v>
       </c>
@@ -4250,33 +4252,33 @@
       <c r="M75" s="69"/>
     </row>
     <row r="76" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="77" t="s">
+      <c r="A76" s="88" t="s">
         <v>119</v>
       </c>
-      <c r="B76" s="78"/>
-      <c r="C76" s="78"/>
-      <c r="D76" s="78"/>
-      <c r="E76" s="78"/>
-      <c r="F76" s="78"/>
-      <c r="G76" s="78"/>
-      <c r="H76" s="78"/>
-      <c r="I76" s="78"/>
-      <c r="J76" s="78"/>
-      <c r="K76" s="78"/>
-      <c r="L76" s="78"/>
-      <c r="M76" s="79"/>
+      <c r="B76" s="89"/>
+      <c r="C76" s="89"/>
+      <c r="D76" s="89"/>
+      <c r="E76" s="89"/>
+      <c r="F76" s="89"/>
+      <c r="G76" s="89"/>
+      <c r="H76" s="89"/>
+      <c r="I76" s="89"/>
+      <c r="J76" s="89"/>
+      <c r="K76" s="89"/>
+      <c r="L76" s="89"/>
+      <c r="M76" s="90"/>
     </row>
     <row r="77" spans="1:13" ht="82.8" x14ac:dyDescent="0.25">
-      <c r="A77" s="86" t="s">
+      <c r="A77" s="77" t="s">
         <v>83</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="C77" s="93" t="s">
+      <c r="C77" s="71" t="s">
         <v>115</v>
       </c>
-      <c r="D77" s="90" t="s">
+      <c r="D77" s="75" t="s">
         <v>128</v>
       </c>
       <c r="E77" s="59">
@@ -4292,12 +4294,12 @@
       <c r="M77" s="69"/>
     </row>
     <row r="78" spans="1:13" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A78" s="86"/>
+      <c r="A78" s="77"/>
       <c r="B78" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C78" s="93"/>
-      <c r="D78" s="95"/>
+      <c r="C78" s="71"/>
+      <c r="D78" s="78"/>
       <c r="E78" s="57">
         <v>50</v>
       </c>
@@ -4311,12 +4313,12 @@
       <c r="M78" s="69"/>
     </row>
     <row r="79" spans="1:13" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A79" s="86"/>
+      <c r="A79" s="77"/>
       <c r="B79" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C79" s="94"/>
-      <c r="D79" s="96"/>
+      <c r="C79" s="72"/>
+      <c r="D79" s="74"/>
       <c r="E79" s="57">
         <v>75</v>
       </c>
@@ -4362,7 +4364,7 @@
       <c r="C81" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D81" s="100" t="s">
+      <c r="D81" s="73" t="s">
         <v>182</v>
       </c>
       <c r="E81" s="57">
@@ -4387,7 +4389,7 @@
       <c r="C82" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="D82" s="96"/>
+      <c r="D82" s="74"/>
       <c r="E82" s="57">
         <v>30</v>
       </c>
@@ -4401,16 +4403,16 @@
       <c r="M82" s="69"/>
     </row>
     <row r="83" spans="1:16" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A83" s="86" t="s">
+      <c r="A83" s="77" t="s">
         <v>90</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C83" s="93" t="s">
+      <c r="C83" s="71" t="s">
         <v>115</v>
       </c>
-      <c r="D83" s="90" t="s">
+      <c r="D83" s="75" t="s">
         <v>183</v>
       </c>
       <c r="E83" s="57">
@@ -4426,12 +4428,12 @@
       <c r="M83" s="69"/>
     </row>
     <row r="84" spans="1:16" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A84" s="86"/>
+      <c r="A84" s="77"/>
       <c r="B84" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C84" s="93"/>
-      <c r="D84" s="90"/>
+      <c r="C84" s="71"/>
+      <c r="D84" s="75"/>
       <c r="E84" s="57">
         <v>50</v>
       </c>
@@ -4445,12 +4447,12 @@
       <c r="M84" s="69"/>
     </row>
     <row r="85" spans="1:16" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A85" s="86"/>
+      <c r="A85" s="77"/>
       <c r="B85" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="C85" s="94"/>
-      <c r="D85" s="90"/>
+      <c r="C85" s="72"/>
+      <c r="D85" s="75"/>
       <c r="E85" s="57">
         <v>35</v>
       </c>
@@ -4473,7 +4475,7 @@
       <c r="C86" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D86" s="90"/>
+      <c r="D86" s="75"/>
       <c r="E86" s="57">
         <v>72</v>
       </c>
@@ -4496,7 +4498,7 @@
       <c r="C87" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="D87" s="91"/>
+      <c r="D87" s="76"/>
       <c r="E87" s="57">
         <v>50</v>
       </c>
@@ -4583,7 +4585,7 @@
       </c>
       <c r="K90" s="54">
         <f t="shared" si="0"/>
-        <v>348</v>
+        <v>508</v>
       </c>
       <c r="L90" s="54">
         <f t="shared" si="0"/>
@@ -5674,43 +5676,6 @@
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="C83:C85"/>
-    <mergeCell ref="D81:D82"/>
-    <mergeCell ref="D83:D87"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="A38:A44"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A55"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="D77:D79"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A63:A66"/>
-    <mergeCell ref="C63:C66"/>
-    <mergeCell ref="D63:D66"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="D50:D51"/>
-    <mergeCell ref="D48:D49"/>
-    <mergeCell ref="C52:C55"/>
-    <mergeCell ref="D52:D55"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="C10:C16"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C38:C44"/>
-    <mergeCell ref="D38:D45"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A32:M32"/>
     <mergeCell ref="A59:M59"/>
     <mergeCell ref="A76:M76"/>
     <mergeCell ref="A2:A3"/>
@@ -5725,6 +5690,43 @@
     <mergeCell ref="C20:C21"/>
     <mergeCell ref="D20:D21"/>
     <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D50:D51"/>
+    <mergeCell ref="D48:D49"/>
+    <mergeCell ref="C52:C55"/>
+    <mergeCell ref="D52:D55"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="C10:C16"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C38:C44"/>
+    <mergeCell ref="D38:D45"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A32:M32"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A63:A66"/>
+    <mergeCell ref="C63:C66"/>
+    <mergeCell ref="D63:D66"/>
+    <mergeCell ref="A38:A44"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A55"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C50:C51"/>
+    <mergeCell ref="C83:C85"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="D83:D87"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="D77:D79"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" copies="0" r:id="rId1"/>

--- a/Kafedra/КЗФ_Наукова_робота_Оліх.xlsx
+++ b/Kafedra/КЗФ_Наукова_робота_Оліх.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DeepL\Kafedra\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Samples\DeepL\Kafedra\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C63D45B-45D0-4403-B837-14EC3F669363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0CD5DDB-B356-46E0-86E3-DBBF9E92AEB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Аркуш1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2175,30 +2175,75 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2217,52 +2262,7 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2559,39 +2559,39 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:V167"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" style="8" customWidth="1"/>
-    <col min="2" max="2" width="42.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="18.88671875" style="4" customWidth="1"/>
-    <col min="4" max="4" width="26.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="19.44140625" style="5" customWidth="1"/>
-    <col min="6" max="7" width="22.5546875" style="13" customWidth="1"/>
-    <col min="8" max="8" width="23.44140625" style="13" customWidth="1"/>
-    <col min="9" max="10" width="22.5546875" style="13" customWidth="1"/>
-    <col min="11" max="11" width="22.5546875" style="14" customWidth="1"/>
-    <col min="12" max="12" width="20.33203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="19.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="7.28515625" style="8" customWidth="1"/>
+    <col min="2" max="2" width="42.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" style="5" customWidth="1"/>
+    <col min="6" max="7" width="22.5703125" style="13" customWidth="1"/>
+    <col min="8" max="8" width="23.42578125" style="13" customWidth="1"/>
+    <col min="9" max="10" width="22.5703125" style="13" customWidth="1"/>
+    <col min="11" max="11" width="22.5703125" style="14" customWidth="1"/>
+    <col min="12" max="12" width="20.28515625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="19.7109375" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" ht="14.45" thickBot="1" x14ac:dyDescent="0.3">
       <c r="K1" s="13"/>
     </row>
-    <row r="2" spans="1:22" s="3" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A2" s="91" t="s">
+    <row r="2" spans="1:22" s="3" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="93" t="s">
+      <c r="B2" s="79" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="94" t="s">
         <v>95</v>
       </c>
-      <c r="D2" s="79" t="s">
+      <c r="D2" s="94" t="s">
         <v>99</v>
       </c>
-      <c r="E2" s="95" t="s">
+      <c r="E2" s="81" t="s">
         <v>1</v>
       </c>
       <c r="F2" s="48" t="s">
@@ -2619,12 +2619,12 @@
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="1:22" s="3" customFormat="1" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="92"/>
-      <c r="B3" s="94"/>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="96"/>
+    <row r="3" spans="1:22" s="3" customFormat="1" ht="34.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="78"/>
+      <c r="B3" s="80"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="82"/>
       <c r="F3" s="23">
         <f>F5*E5+F6*E6+F7*E7+F8*E8+F9*E9+F10*E10+F11*E11+F12*E12+F13*E13+F14*E14+F15*E15+F16*E16+F17*E17+F18*E18+F19*E19+F20*E20+F21*E21+F22*E22+F23*E23+F24*E24+F25*E25+F26*E26+F27*E27+F28*E28+F29*E29+F30*E30+F31*E31+F33*E33+F34*E34+F35*E35+F36*E36+F37*E37+F38*E38+F39*E39+F40*E40+F41*E41+F42*E42+F43*E43+F44*E44+F45*E45+F46*E46+F47*E47+F48*E48+F49*E49+F50*E50+F51*E51+F52*E52+F53*E53+F54*E54+F55*E55+F56*E56+F57*E57+F58*E58+F60*E60+F61*E61+F62*E62+F63*E63+F64*E64+F65*E65+F66*E66+F67*E67+F68*E68+F69*E69+F70*E70+F71*E71+F72*E72+F73*E73+F74*E74+F75*E75+F77*E77+F78*E78+F79*E79+F80*E80+F81*E81+F82*E82+F83*E83+F84*E84+F85*E85+F86*E86+F87*E87+F88*E88+F89*E89</f>
         <v>0</v>
@@ -2647,7 +2647,7 @@
       </c>
       <c r="K3" s="25">
         <f>K5*$E5+K6*$E6+K7*$E7+K8*$E8+K9*$E9+K10*$E10+K11*$E11+K12*$E12+K13*$E13+K14*$E14+K15*$E15+K16*$E16+K17*$E17+K18*$E18+K19*$E19+K20*$E20+K21*$E21+K22*$E22+K23*$E23+K24*$E24+K25*$E25+K26*$E26+K27*$E27+K28*$E28+K29*$E29+K30*$E30+K31*$E31+K33*$E33+K34*$E34+K35*$E35+K36*$E36+K37*$E37+K38*$E38+K39*$E39+K40*$E40+K41*$E41+K42*$E42+K43*$E43+K44*$E44+K45*$E45+K46*$E46+K47*$E47+K48*$E48+K49*$E49+K50*$E50+K51*$E51+K52*$E52+K53*$E53+K54*$E54+K55*$E55+K56*$E56+K57*$E57+K58*$E58+K60*$E60+K61*$E61+K62*$E62+K63*$E63+K64*$E64+K65*$E65+K66*$E66+K67*$E67+K68*$E68+K69*$E69+K70*$E70+K71*$E71+K72*$E72+K73*$E73+K74*$E74+K75*$E75+K77*$E77+K78*$E78+K79*$E79+K80*$E80+K81*$E81+K82*$E82+K83*$E83+K84*$E84+K85*$E85+K86*$E86+K87*$E87+K88*$E88+K89*$E89</f>
-        <v>508</v>
+        <v>583</v>
       </c>
       <c r="L3" s="62">
         <f>L5*$E5+L6*$E6+L7*$E7+L8*$E8+L9*$E9+L10*$E10+L11*$E11+L12*$E12+L13*$E13+L14*$E14+L15*$E15+L16*$E16+L17*$E17+L18*$E18+L19*$E19+L20*$E20+L21*$E21+L22*$E22+L23*$E23+L24*$E24+L25*$E25+L26*$E26+L27*$E27+L28*$E28+L29*$E29+L30*$E30+L31*$E31+L33*$E33+L34*$E34+L35*$E35+L36*$E36+L37*$E37+L38*$E38+L39*$E39+L40*$E40+L41*$E41+L42*$E42+L43*$E43+L44*$E44+L45*$E45+L46*$E46+L47*$E47+L48*$E48+L49*$E49+L50*$E50+L51*$E51+L52*$E52+L53*$E53+L54*$E54+L55*$E55+L56*$E56+L57*$E57+L58*$E58+L60*$E60+L61*$E61+L62*$E62+L63*$E63+L64*$E64+L65*$E65+L66*$E66+L67*$E67+L68*$E68+L69*$E69+L70*$E70+L71*$E71+L72*$E72+L73*$E73+L74*$E74+L75*$E75+L77*$E77+L78*$E78+L79*$E79+L80*$E80+L81*$E81+L82*$E82+L83*$E83+L84*$E84+L85*$E85+L86*$E86+L87*$E87+L88*$E88+L89*$E89</f>
@@ -2658,22 +2658,22 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:22" s="3" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="82" t="s">
+    <row r="4" spans="1:22" s="3" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="84"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="99"/>
       <c r="N4" s="60"/>
       <c r="O4" s="60"/>
       <c r="P4" s="60"/>
@@ -2684,17 +2684,17 @@
       <c r="U4" s="60"/>
       <c r="V4" s="60"/>
     </row>
-    <row r="5" spans="1:22" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" ht="73.5" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="20" t="s">
         <v>138</v>
       </c>
-      <c r="C5" s="100" t="s">
+      <c r="C5" s="89" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="99" t="s">
+      <c r="D5" s="86" t="s">
         <v>120</v>
       </c>
       <c r="E5" s="55">
@@ -2709,15 +2709,15 @@
       <c r="L5" s="63"/>
       <c r="M5" s="68"/>
     </row>
-    <row r="6" spans="1:22" ht="151.80000000000001" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:22" ht="162" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="C6" s="71"/>
-      <c r="D6" s="75"/>
+      <c r="C6" s="90"/>
+      <c r="D6" s="87"/>
       <c r="E6" s="56">
         <v>100</v>
       </c>
@@ -2732,15 +2732,15 @@
       <c r="L6" s="64"/>
       <c r="M6" s="69"/>
     </row>
-    <row r="7" spans="1:22" ht="82.8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="C7" s="72"/>
-      <c r="D7" s="75"/>
+      <c r="C7" s="91"/>
+      <c r="D7" s="87"/>
       <c r="E7" s="56">
         <v>100</v>
       </c>
@@ -2753,7 +2753,7 @@
       <c r="L7" s="64"/>
       <c r="M7" s="69"/>
     </row>
-    <row r="8" spans="1:22" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" ht="45" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>13</v>
       </c>
@@ -2763,7 +2763,7 @@
       <c r="C8" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D8" s="76"/>
+      <c r="D8" s="88"/>
       <c r="E8" s="56">
         <v>75</v>
       </c>
@@ -2776,7 +2776,7 @@
       <c r="L8" s="64"/>
       <c r="M8" s="69"/>
     </row>
-    <row r="9" spans="1:22" ht="48" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" ht="57" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>14</v>
       </c>
@@ -2801,14 +2801,14 @@
       <c r="L9" s="64"/>
       <c r="M9" s="69"/>
     </row>
-    <row r="10" spans="1:22" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A10" s="77" t="s">
+    <row r="10" spans="1:22" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A10" s="83" t="s">
         <v>15</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="81" t="s">
+      <c r="C10" s="96" t="s">
         <v>100</v>
       </c>
       <c r="D10" s="46" t="s">
@@ -2826,13 +2826,13 @@
       <c r="L10" s="64"/>
       <c r="M10" s="69"/>
     </row>
-    <row r="11" spans="1:22" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A11" s="77"/>
+    <row r="11" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="83"/>
       <c r="B11" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="71"/>
-      <c r="D11" s="75" t="s">
+      <c r="C11" s="90"/>
+      <c r="D11" s="87" t="s">
         <v>131</v>
       </c>
       <c r="E11" s="57">
@@ -2847,13 +2847,13 @@
       <c r="L11" s="64"/>
       <c r="M11" s="69"/>
     </row>
-    <row r="12" spans="1:22" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A12" s="77"/>
+    <row r="12" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="83"/>
       <c r="B12" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="71"/>
-      <c r="D12" s="75"/>
+      <c r="C12" s="90"/>
+      <c r="D12" s="87"/>
       <c r="E12" s="57">
         <v>200</v>
       </c>
@@ -2862,19 +2862,17 @@
       <c r="H12" s="34"/>
       <c r="I12" s="37"/>
       <c r="J12" s="40"/>
-      <c r="K12" s="43">
-        <v>1</v>
-      </c>
+      <c r="K12" s="43"/>
       <c r="L12" s="64"/>
       <c r="M12" s="69"/>
     </row>
-    <row r="13" spans="1:22" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A13" s="77"/>
+    <row r="13" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="83"/>
       <c r="B13" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="71"/>
-      <c r="D13" s="75"/>
+      <c r="C13" s="90"/>
+      <c r="D13" s="87"/>
       <c r="E13" s="57">
         <v>150</v>
       </c>
@@ -2883,17 +2881,19 @@
       <c r="H13" s="34"/>
       <c r="I13" s="37"/>
       <c r="J13" s="40"/>
-      <c r="K13" s="43"/>
+      <c r="K13" s="43">
+        <v>1</v>
+      </c>
       <c r="L13" s="64"/>
       <c r="M13" s="69"/>
     </row>
-    <row r="14" spans="1:22" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A14" s="77"/>
+    <row r="14" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="83"/>
       <c r="B14" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="71"/>
-      <c r="D14" s="75"/>
+      <c r="C14" s="90"/>
+      <c r="D14" s="87"/>
       <c r="E14" s="57">
         <v>125</v>
       </c>
@@ -2902,17 +2902,19 @@
       <c r="H14" s="34"/>
       <c r="I14" s="37"/>
       <c r="J14" s="40"/>
-      <c r="K14" s="43"/>
+      <c r="K14" s="43">
+        <v>1</v>
+      </c>
       <c r="L14" s="64"/>
       <c r="M14" s="69"/>
     </row>
-    <row r="15" spans="1:22" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A15" s="77"/>
+    <row r="15" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="83"/>
       <c r="B15" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="C15" s="71"/>
-      <c r="D15" s="75"/>
+      <c r="C15" s="90"/>
+      <c r="D15" s="87"/>
       <c r="E15" s="57">
         <v>100</v>
       </c>
@@ -2926,12 +2928,12 @@
       <c r="M15" s="69"/>
     </row>
     <row r="16" spans="1:22" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="77"/>
+      <c r="A16" s="83"/>
       <c r="B16" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C16" s="72"/>
-      <c r="D16" s="76"/>
+      <c r="C16" s="91"/>
+      <c r="D16" s="88"/>
       <c r="E16" s="57">
         <v>100</v>
       </c>
@@ -2944,7 +2946,7 @@
       <c r="L16" s="64"/>
       <c r="M16" s="69"/>
     </row>
-    <row r="17" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>16</v>
       </c>
@@ -2967,17 +2969,17 @@
       <c r="L17" s="64"/>
       <c r="M17" s="69"/>
     </row>
-    <row r="18" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A18" s="97" t="s">
+    <row r="18" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="84" t="s">
         <v>17</v>
       </c>
       <c r="B18" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C18" s="71" t="s">
+      <c r="C18" s="90" t="s">
         <v>102</v>
       </c>
-      <c r="D18" s="78"/>
+      <c r="D18" s="92"/>
       <c r="E18" s="59">
         <v>150</v>
       </c>
@@ -2990,13 +2992,13 @@
       <c r="L18" s="64"/>
       <c r="M18" s="69"/>
     </row>
-    <row r="19" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A19" s="98"/>
+    <row r="19" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="85"/>
       <c r="B19" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C19" s="72"/>
-      <c r="D19" s="74"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="93"/>
       <c r="E19" s="57">
         <v>100</v>
       </c>
@@ -3009,17 +3011,17 @@
       <c r="L19" s="64"/>
       <c r="M19" s="69"/>
     </row>
-    <row r="20" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A20" s="77" t="s">
+    <row r="20" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="83" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="C20" s="71" t="s">
+      <c r="C20" s="90" t="s">
         <v>102</v>
       </c>
-      <c r="D20" s="78"/>
+      <c r="D20" s="92"/>
       <c r="E20" s="59">
         <v>100</v>
       </c>
@@ -3032,13 +3034,13 @@
       <c r="L20" s="64"/>
       <c r="M20" s="69"/>
     </row>
-    <row r="21" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A21" s="77"/>
+    <row r="21" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="83"/>
       <c r="B21" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C21" s="72"/>
-      <c r="D21" s="74"/>
+      <c r="C21" s="91"/>
+      <c r="D21" s="93"/>
       <c r="E21" s="57">
         <v>50</v>
       </c>
@@ -3051,7 +3053,7 @@
       <c r="L21" s="64"/>
       <c r="M21" s="69"/>
     </row>
-    <row r="22" spans="1:13" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="44.25" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>19</v>
       </c>
@@ -3097,7 +3099,7 @@
       <c r="L23" s="64"/>
       <c r="M23" s="69"/>
     </row>
-    <row r="24" spans="1:13" ht="82.8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>21</v>
       </c>
@@ -3122,7 +3124,7 @@
       <c r="L24" s="64"/>
       <c r="M24" s="69"/>
     </row>
-    <row r="25" spans="1:13" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
         <v>22</v>
       </c>
@@ -3168,7 +3170,7 @@
       <c r="L26" s="64"/>
       <c r="M26" s="69"/>
     </row>
-    <row r="27" spans="1:13" ht="69" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
         <v>24</v>
       </c>
@@ -3216,7 +3218,7 @@
       <c r="L28" s="64"/>
       <c r="M28" s="69"/>
     </row>
-    <row r="29" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="36" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>26</v>
       </c>
@@ -3241,7 +3243,7 @@
       <c r="L29" s="64"/>
       <c r="M29" s="69"/>
     </row>
-    <row r="30" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="72" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>27</v>
       </c>
@@ -3268,7 +3270,7 @@
       <c r="L30" s="64"/>
       <c r="M30" s="69"/>
     </row>
-    <row r="31" spans="1:13" ht="151.80000000000001" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="171" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
         <v>28</v>
       </c>
@@ -3291,24 +3293,24 @@
       <c r="L31" s="64"/>
       <c r="M31" s="69"/>
     </row>
-    <row r="32" spans="1:13" s="3" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="85" t="s">
+    <row r="32" spans="1:13" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="86"/>
-      <c r="C32" s="86"/>
-      <c r="D32" s="86"/>
-      <c r="E32" s="86"/>
-      <c r="F32" s="86"/>
-      <c r="G32" s="86"/>
-      <c r="H32" s="86"/>
-      <c r="I32" s="86"/>
-      <c r="J32" s="86"/>
-      <c r="K32" s="86"/>
-      <c r="L32" s="86"/>
-      <c r="M32" s="87"/>
-    </row>
-    <row r="33" spans="1:13" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B32" s="72"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="72"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="72"/>
+      <c r="L32" s="72"/>
+      <c r="M32" s="73"/>
+    </row>
+    <row r="33" spans="1:13" ht="44.25" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>8</v>
       </c>
@@ -3377,7 +3379,7 @@
       <c r="L35" s="64"/>
       <c r="M35" s="69"/>
     </row>
-    <row r="36" spans="1:13" ht="69" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="88.5" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
         <v>32</v>
       </c>
@@ -3400,7 +3402,7 @@
       <c r="L36" s="64"/>
       <c r="M36" s="69"/>
     </row>
-    <row r="37" spans="1:13" ht="69" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="85.5" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
         <v>33</v>
       </c>
@@ -3425,17 +3427,17 @@
       <c r="L37" s="64"/>
       <c r="M37" s="69"/>
     </row>
-    <row r="38" spans="1:13" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A38" s="77" t="s">
+    <row r="38" spans="1:13" ht="73.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="83" t="s">
         <v>34</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C38" s="71" t="s">
+      <c r="C38" s="90" t="s">
         <v>104</v>
       </c>
-      <c r="D38" s="75" t="s">
+      <c r="D38" s="87" t="s">
         <v>179</v>
       </c>
       <c r="E38" s="59">
@@ -3450,13 +3452,13 @@
       <c r="L38" s="64"/>
       <c r="M38" s="69"/>
     </row>
-    <row r="39" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A39" s="77"/>
+    <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A39" s="83"/>
       <c r="B39" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C39" s="71"/>
-      <c r="D39" s="75"/>
+      <c r="C39" s="90"/>
+      <c r="D39" s="87"/>
       <c r="E39" s="57">
         <v>50</v>
       </c>
@@ -3469,13 +3471,13 @@
       <c r="L39" s="64"/>
       <c r="M39" s="69"/>
     </row>
-    <row r="40" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A40" s="77"/>
+    <row r="40" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="83"/>
       <c r="B40" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C40" s="71"/>
-      <c r="D40" s="75"/>
+      <c r="C40" s="90"/>
+      <c r="D40" s="87"/>
       <c r="E40" s="57">
         <v>100</v>
       </c>
@@ -3488,13 +3490,13 @@
       <c r="L40" s="64"/>
       <c r="M40" s="69"/>
     </row>
-    <row r="41" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A41" s="77"/>
+    <row r="41" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A41" s="83"/>
       <c r="B41" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C41" s="71"/>
-      <c r="D41" s="75"/>
+      <c r="C41" s="90"/>
+      <c r="D41" s="87"/>
       <c r="E41" s="57">
         <v>75</v>
       </c>
@@ -3507,13 +3509,13 @@
       <c r="L41" s="64"/>
       <c r="M41" s="69"/>
     </row>
-    <row r="42" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A42" s="77"/>
+    <row r="42" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="83"/>
       <c r="B42" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="71"/>
-      <c r="D42" s="75"/>
+      <c r="C42" s="90"/>
+      <c r="D42" s="87"/>
       <c r="E42" s="57">
         <v>100</v>
       </c>
@@ -3526,13 +3528,13 @@
       <c r="L42" s="64"/>
       <c r="M42" s="69"/>
     </row>
-    <row r="43" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A43" s="77"/>
+    <row r="43" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="83"/>
       <c r="B43" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="71"/>
-      <c r="D43" s="75"/>
+      <c r="C43" s="90"/>
+      <c r="D43" s="87"/>
       <c r="E43" s="57">
         <v>75</v>
       </c>
@@ -3545,13 +3547,13 @@
       <c r="L43" s="64"/>
       <c r="M43" s="69"/>
     </row>
-    <row r="44" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A44" s="77"/>
+    <row r="44" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A44" s="83"/>
       <c r="B44" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C44" s="72"/>
-      <c r="D44" s="75"/>
+      <c r="C44" s="91"/>
+      <c r="D44" s="87"/>
       <c r="E44" s="57">
         <v>50</v>
       </c>
@@ -3564,7 +3566,7 @@
       <c r="L44" s="64"/>
       <c r="M44" s="69"/>
     </row>
-    <row r="45" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>35</v>
       </c>
@@ -3574,7 +3576,7 @@
       <c r="C45" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="D45" s="76"/>
+      <c r="D45" s="88"/>
       <c r="E45" s="57">
         <v>10</v>
       </c>
@@ -3637,17 +3639,17 @@
       <c r="L47" s="64"/>
       <c r="M47" s="69"/>
     </row>
-    <row r="48" spans="1:13" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A48" s="77" t="s">
+    <row r="48" spans="1:13" ht="72.75" x14ac:dyDescent="0.25">
+      <c r="A48" s="83" t="s">
         <v>40</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="C48" s="71" t="s">
+      <c r="C48" s="90" t="s">
         <v>108</v>
       </c>
-      <c r="D48" s="75" t="s">
+      <c r="D48" s="87" t="s">
         <v>125</v>
       </c>
       <c r="E48" s="59">
@@ -3664,13 +3666,13 @@
       <c r="L48" s="64"/>
       <c r="M48" s="69"/>
     </row>
-    <row r="49" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A49" s="77"/>
+    <row r="49" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A49" s="83"/>
       <c r="B49" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C49" s="72"/>
-      <c r="D49" s="76"/>
+      <c r="C49" s="91"/>
+      <c r="D49" s="88"/>
       <c r="E49" s="57">
         <v>30</v>
       </c>
@@ -3683,17 +3685,17 @@
       <c r="L49" s="64"/>
       <c r="M49" s="69"/>
     </row>
-    <row r="50" spans="1:13" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A50" s="77" t="s">
+    <row r="50" spans="1:13" ht="59.25" x14ac:dyDescent="0.25">
+      <c r="A50" s="83" t="s">
         <v>41</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="C50" s="71" t="s">
+      <c r="C50" s="90" t="s">
         <v>103</v>
       </c>
-      <c r="D50" s="75" t="s">
+      <c r="D50" s="87" t="s">
         <v>125</v>
       </c>
       <c r="E50" s="59">
@@ -3709,12 +3711,12 @@
       <c r="M50" s="69"/>
     </row>
     <row r="51" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="77"/>
+      <c r="A51" s="83"/>
       <c r="B51" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="C51" s="72"/>
-      <c r="D51" s="76"/>
+      <c r="C51" s="91"/>
+      <c r="D51" s="88"/>
       <c r="E51" s="57">
         <v>40</v>
       </c>
@@ -3727,17 +3729,17 @@
       <c r="L51" s="64"/>
       <c r="M51" s="69"/>
     </row>
-    <row r="52" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A52" s="77" t="s">
+    <row r="52" spans="1:13" ht="44.25" x14ac:dyDescent="0.25">
+      <c r="A52" s="83" t="s">
         <v>60</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="C52" s="71" t="s">
+      <c r="C52" s="90" t="s">
         <v>134</v>
       </c>
-      <c r="D52" s="75" t="s">
+      <c r="D52" s="87" t="s">
         <v>180</v>
       </c>
       <c r="E52" s="59">
@@ -3752,13 +3754,13 @@
       <c r="L52" s="64"/>
       <c r="M52" s="69"/>
     </row>
-    <row r="53" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A53" s="77"/>
+    <row r="53" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A53" s="83"/>
       <c r="B53" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="71"/>
-      <c r="D53" s="75"/>
+      <c r="C53" s="90"/>
+      <c r="D53" s="87"/>
       <c r="E53" s="57">
         <v>8</v>
       </c>
@@ -3771,13 +3773,13 @@
       <c r="L53" s="64"/>
       <c r="M53" s="69"/>
     </row>
-    <row r="54" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A54" s="77"/>
+    <row r="54" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A54" s="83"/>
       <c r="B54" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C54" s="71"/>
-      <c r="D54" s="75"/>
+      <c r="C54" s="90"/>
+      <c r="D54" s="87"/>
       <c r="E54" s="57">
         <v>12</v>
       </c>
@@ -3790,13 +3792,13 @@
       <c r="L54" s="64"/>
       <c r="M54" s="69"/>
     </row>
-    <row r="55" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A55" s="77"/>
+    <row r="55" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A55" s="83"/>
       <c r="B55" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C55" s="72"/>
-      <c r="D55" s="76"/>
+      <c r="C55" s="91"/>
+      <c r="D55" s="88"/>
       <c r="E55" s="57">
         <v>6</v>
       </c>
@@ -3811,7 +3813,7 @@
       <c r="L55" s="64"/>
       <c r="M55" s="69"/>
     </row>
-    <row r="56" spans="1:13" ht="138" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" ht="156.75" x14ac:dyDescent="0.25">
       <c r="A56" s="15" t="s">
         <v>61</v>
       </c>
@@ -3836,7 +3838,7 @@
       <c r="L56" s="64"/>
       <c r="M56" s="69"/>
     </row>
-    <row r="57" spans="1:13" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="59.25" x14ac:dyDescent="0.25">
       <c r="A57" s="15" t="s">
         <v>62</v>
       </c>
@@ -3859,7 +3861,7 @@
       <c r="L57" s="64"/>
       <c r="M57" s="69"/>
     </row>
-    <row r="58" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>63</v>
       </c>
@@ -3882,24 +3884,24 @@
       <c r="L58" s="64"/>
       <c r="M58" s="69"/>
     </row>
-    <row r="59" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A59" s="85" t="s">
+    <row r="59" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="71" t="s">
         <v>65</v>
       </c>
-      <c r="B59" s="86"/>
-      <c r="C59" s="86"/>
-      <c r="D59" s="86"/>
-      <c r="E59" s="86"/>
-      <c r="F59" s="86"/>
-      <c r="G59" s="86"/>
-      <c r="H59" s="86"/>
-      <c r="I59" s="86"/>
-      <c r="J59" s="86"/>
-      <c r="K59" s="86"/>
-      <c r="L59" s="86"/>
-      <c r="M59" s="87"/>
-    </row>
-    <row r="60" spans="1:13" ht="41.4" x14ac:dyDescent="0.25">
+      <c r="B59" s="72"/>
+      <c r="C59" s="72"/>
+      <c r="D59" s="72"/>
+      <c r="E59" s="72"/>
+      <c r="F59" s="72"/>
+      <c r="G59" s="72"/>
+      <c r="H59" s="72"/>
+      <c r="I59" s="72"/>
+      <c r="J59" s="72"/>
+      <c r="K59" s="72"/>
+      <c r="L59" s="72"/>
+      <c r="M59" s="73"/>
+    </row>
+    <row r="60" spans="1:13" ht="44.25" x14ac:dyDescent="0.25">
       <c r="A60" s="15" t="s">
         <v>67</v>
       </c>
@@ -3924,17 +3926,17 @@
       <c r="L60" s="64"/>
       <c r="M60" s="69"/>
     </row>
-    <row r="61" spans="1:13" ht="69" x14ac:dyDescent="0.25">
-      <c r="A61" s="77" t="s">
+    <row r="61" spans="1:13" ht="74.25" x14ac:dyDescent="0.25">
+      <c r="A61" s="83" t="s">
         <v>68</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="C61" s="71" t="s">
+      <c r="C61" s="90" t="s">
         <v>101</v>
       </c>
-      <c r="D61" s="75" t="s">
+      <c r="D61" s="87" t="s">
         <v>127</v>
       </c>
       <c r="E61" s="59">
@@ -3949,13 +3951,13 @@
       <c r="L61" s="64"/>
       <c r="M61" s="69"/>
     </row>
-    <row r="62" spans="1:13" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A62" s="77"/>
+    <row r="62" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A62" s="83"/>
       <c r="B62" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="C62" s="72"/>
-      <c r="D62" s="76"/>
+      <c r="C62" s="91"/>
+      <c r="D62" s="88"/>
       <c r="E62" s="57">
         <v>5</v>
       </c>
@@ -3968,15 +3970,15 @@
       <c r="L62" s="64"/>
       <c r="M62" s="69"/>
     </row>
-    <row r="63" spans="1:13" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A63" s="77"/>
+    <row r="63" spans="1:13" ht="59.25" x14ac:dyDescent="0.25">
+      <c r="A63" s="83"/>
       <c r="B63" s="12" t="s">
         <v>176</v>
       </c>
-      <c r="C63" s="71" t="s">
+      <c r="C63" s="90" t="s">
         <v>135</v>
       </c>
-      <c r="D63" s="75" t="s">
+      <c r="D63" s="87" t="s">
         <v>132</v>
       </c>
       <c r="E63" s="59">
@@ -3991,13 +3993,13 @@
       <c r="L63" s="64"/>
       <c r="M63" s="69"/>
     </row>
-    <row r="64" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A64" s="77"/>
+    <row r="64" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A64" s="83"/>
       <c r="B64" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C64" s="71"/>
-      <c r="D64" s="75"/>
+      <c r="C64" s="90"/>
+      <c r="D64" s="87"/>
       <c r="E64" s="57">
         <v>30</v>
       </c>
@@ -4010,13 +4012,13 @@
       <c r="L64" s="64"/>
       <c r="M64" s="69"/>
     </row>
-    <row r="65" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A65" s="77"/>
+    <row r="65" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="83"/>
       <c r="B65" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="C65" s="71"/>
-      <c r="D65" s="75"/>
+      <c r="C65" s="90"/>
+      <c r="D65" s="87"/>
       <c r="E65" s="57">
         <v>50</v>
       </c>
@@ -4029,13 +4031,13 @@
       <c r="L65" s="64"/>
       <c r="M65" s="69"/>
     </row>
-    <row r="66" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A66" s="77"/>
+    <row r="66" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="83"/>
       <c r="B66" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C66" s="72"/>
-      <c r="D66" s="76"/>
+      <c r="C66" s="91"/>
+      <c r="D66" s="88"/>
       <c r="E66" s="57">
         <v>30</v>
       </c>
@@ -4048,7 +4050,7 @@
       <c r="L66" s="64"/>
       <c r="M66" s="69"/>
     </row>
-    <row r="67" spans="1:13" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A67" s="15" t="s">
         <v>71</v>
       </c>
@@ -4071,7 +4073,7 @@
       <c r="L67" s="64"/>
       <c r="M67" s="69"/>
     </row>
-    <row r="68" spans="1:13" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="59.25" x14ac:dyDescent="0.25">
       <c r="A68" s="15" t="s">
         <v>72</v>
       </c>
@@ -4094,7 +4096,7 @@
       <c r="L68" s="64"/>
       <c r="M68" s="69"/>
     </row>
-    <row r="69" spans="1:13" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="58.5" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
         <v>74</v>
       </c>
@@ -4119,17 +4121,17 @@
       <c r="L69" s="64"/>
       <c r="M69" s="69"/>
     </row>
-    <row r="70" spans="1:13" ht="55.2" x14ac:dyDescent="0.25">
-      <c r="A70" s="77" t="s">
+    <row r="70" spans="1:13" ht="58.5" x14ac:dyDescent="0.25">
+      <c r="A70" s="83" t="s">
         <v>76</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="C70" s="71" t="s">
+      <c r="C70" s="90" t="s">
         <v>112</v>
       </c>
-      <c r="D70" s="78"/>
+      <c r="D70" s="92"/>
       <c r="E70" s="59">
         <v>2</v>
       </c>
@@ -4142,13 +4144,13 @@
       <c r="L70" s="64"/>
       <c r="M70" s="69"/>
     </row>
-    <row r="71" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A71" s="77"/>
+    <row r="71" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="83"/>
       <c r="B71" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C71" s="72"/>
-      <c r="D71" s="74"/>
+      <c r="C71" s="91"/>
+      <c r="D71" s="93"/>
       <c r="E71" s="57">
         <v>4</v>
       </c>
@@ -4163,17 +4165,17 @@
       <c r="L71" s="64"/>
       <c r="M71" s="69"/>
     </row>
-    <row r="72" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A72" s="77" t="s">
+    <row r="72" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="A72" s="83" t="s">
         <v>77</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="C72" s="71" t="s">
+      <c r="C72" s="90" t="s">
         <v>113</v>
       </c>
-      <c r="D72" s="78"/>
+      <c r="D72" s="92"/>
       <c r="E72" s="59">
         <v>2</v>
       </c>
@@ -4186,13 +4188,13 @@
       <c r="L72" s="64"/>
       <c r="M72" s="69"/>
     </row>
-    <row r="73" spans="1:13" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A73" s="77"/>
+    <row r="73" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="83"/>
       <c r="B73" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C73" s="72"/>
-      <c r="D73" s="74"/>
+      <c r="C73" s="91"/>
+      <c r="D73" s="93"/>
       <c r="E73" s="57">
         <v>4</v>
       </c>
@@ -4205,7 +4207,7 @@
       <c r="L73" s="64"/>
       <c r="M73" s="69"/>
     </row>
-    <row r="74" spans="1:13" ht="27.6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
         <v>79</v>
       </c>
@@ -4228,7 +4230,7 @@
       <c r="L74" s="64"/>
       <c r="M74" s="69"/>
     </row>
-    <row r="75" spans="1:13" ht="69" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" ht="71.25" x14ac:dyDescent="0.25">
       <c r="A75" s="15" t="s">
         <v>80</v>
       </c>
@@ -4252,33 +4254,33 @@
       <c r="M75" s="69"/>
     </row>
     <row r="76" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="88" t="s">
+      <c r="A76" s="74" t="s">
         <v>119</v>
       </c>
-      <c r="B76" s="89"/>
-      <c r="C76" s="89"/>
-      <c r="D76" s="89"/>
-      <c r="E76" s="89"/>
-      <c r="F76" s="89"/>
-      <c r="G76" s="89"/>
-      <c r="H76" s="89"/>
-      <c r="I76" s="89"/>
-      <c r="J76" s="89"/>
-      <c r="K76" s="89"/>
-      <c r="L76" s="89"/>
-      <c r="M76" s="90"/>
-    </row>
-    <row r="77" spans="1:13" ht="82.8" x14ac:dyDescent="0.25">
-      <c r="A77" s="77" t="s">
+      <c r="B76" s="75"/>
+      <c r="C76" s="75"/>
+      <c r="D76" s="75"/>
+      <c r="E76" s="75"/>
+      <c r="F76" s="75"/>
+      <c r="G76" s="75"/>
+      <c r="H76" s="75"/>
+      <c r="I76" s="75"/>
+      <c r="J76" s="75"/>
+      <c r="K76" s="75"/>
+      <c r="L76" s="75"/>
+      <c r="M76" s="76"/>
+    </row>
+    <row r="77" spans="1:13" ht="89.25" x14ac:dyDescent="0.25">
+      <c r="A77" s="83" t="s">
         <v>83</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>163</v>
       </c>
-      <c r="C77" s="71" t="s">
+      <c r="C77" s="90" t="s">
         <v>115</v>
       </c>
-      <c r="D77" s="75" t="s">
+      <c r="D77" s="87" t="s">
         <v>128</v>
       </c>
       <c r="E77" s="59">
@@ -4293,13 +4295,13 @@
       <c r="L77" s="64"/>
       <c r="M77" s="69"/>
     </row>
-    <row r="78" spans="1:13" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A78" s="77"/>
+    <row r="78" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A78" s="83"/>
       <c r="B78" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="C78" s="71"/>
-      <c r="D78" s="78"/>
+      <c r="C78" s="90"/>
+      <c r="D78" s="92"/>
       <c r="E78" s="57">
         <v>50</v>
       </c>
@@ -4312,13 +4314,13 @@
       <c r="L78" s="64"/>
       <c r="M78" s="69"/>
     </row>
-    <row r="79" spans="1:13" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A79" s="77"/>
+    <row r="79" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+      <c r="A79" s="83"/>
       <c r="B79" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="C79" s="72"/>
-      <c r="D79" s="74"/>
+      <c r="C79" s="91"/>
+      <c r="D79" s="93"/>
       <c r="E79" s="57">
         <v>75</v>
       </c>
@@ -4331,7 +4333,7 @@
       <c r="L79" s="64"/>
       <c r="M79" s="69"/>
     </row>
-    <row r="80" spans="1:13" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" ht="44.25" x14ac:dyDescent="0.25">
       <c r="A80" s="15" t="s">
         <v>84</v>
       </c>
@@ -4354,7 +4356,7 @@
       <c r="L80" s="64"/>
       <c r="M80" s="69"/>
     </row>
-    <row r="81" spans="1:16" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:16" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="15" t="s">
         <v>87</v>
       </c>
@@ -4364,7 +4366,7 @@
       <c r="C81" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D81" s="73" t="s">
+      <c r="D81" s="100" t="s">
         <v>182</v>
       </c>
       <c r="E81" s="57">
@@ -4379,7 +4381,7 @@
       <c r="L81" s="64"/>
       <c r="M81" s="69"/>
     </row>
-    <row r="82" spans="1:16" ht="69" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" ht="74.25" x14ac:dyDescent="0.25">
       <c r="A82" s="15" t="s">
         <v>88</v>
       </c>
@@ -4389,7 +4391,7 @@
       <c r="C82" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="D82" s="74"/>
+      <c r="D82" s="93"/>
       <c r="E82" s="57">
         <v>30</v>
       </c>
@@ -4402,17 +4404,17 @@
       <c r="L82" s="64"/>
       <c r="M82" s="69"/>
     </row>
-    <row r="83" spans="1:16" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A83" s="77" t="s">
+    <row r="83" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+      <c r="A83" s="83" t="s">
         <v>90</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>164</v>
       </c>
-      <c r="C83" s="71" t="s">
+      <c r="C83" s="90" t="s">
         <v>115</v>
       </c>
-      <c r="D83" s="75" t="s">
+      <c r="D83" s="87" t="s">
         <v>183</v>
       </c>
       <c r="E83" s="57">
@@ -4427,13 +4429,13 @@
       <c r="L83" s="64"/>
       <c r="M83" s="69"/>
     </row>
-    <row r="84" spans="1:16" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A84" s="77"/>
+    <row r="84" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A84" s="83"/>
       <c r="B84" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="C84" s="71"/>
-      <c r="D84" s="75"/>
+      <c r="C84" s="90"/>
+      <c r="D84" s="87"/>
       <c r="E84" s="57">
         <v>50</v>
       </c>
@@ -4446,13 +4448,13 @@
       <c r="L84" s="64"/>
       <c r="M84" s="69"/>
     </row>
-    <row r="85" spans="1:16" ht="41.4" x14ac:dyDescent="0.25">
-      <c r="A85" s="77"/>
+    <row r="85" spans="1:16" ht="45" x14ac:dyDescent="0.25">
+      <c r="A85" s="83"/>
       <c r="B85" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="C85" s="72"/>
-      <c r="D85" s="75"/>
+      <c r="C85" s="91"/>
+      <c r="D85" s="87"/>
       <c r="E85" s="57">
         <v>35</v>
       </c>
@@ -4465,7 +4467,7 @@
       <c r="L85" s="64"/>
       <c r="M85" s="69"/>
     </row>
-    <row r="86" spans="1:16" ht="41.4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" ht="44.25" x14ac:dyDescent="0.25">
       <c r="A86" s="15" t="s">
         <v>91</v>
       </c>
@@ -4475,7 +4477,7 @@
       <c r="C86" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="D86" s="75"/>
+      <c r="D86" s="87"/>
       <c r="E86" s="57">
         <v>72</v>
       </c>
@@ -4488,7 +4490,7 @@
       <c r="L86" s="64"/>
       <c r="M86" s="69"/>
     </row>
-    <row r="87" spans="1:16" ht="82.8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A87" s="15" t="s">
         <v>93</v>
       </c>
@@ -4498,7 +4500,7 @@
       <c r="C87" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="D87" s="76"/>
+      <c r="D87" s="88"/>
       <c r="E87" s="57">
         <v>50</v>
       </c>
@@ -4511,7 +4513,7 @@
       <c r="L87" s="64"/>
       <c r="M87" s="69"/>
     </row>
-    <row r="88" spans="1:16" ht="55.2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" ht="57" x14ac:dyDescent="0.25">
       <c r="A88" s="15" t="s">
         <v>94</v>
       </c>
@@ -4561,7 +4563,7 @@
       <c r="L89" s="65"/>
       <c r="M89" s="70"/>
     </row>
-    <row r="90" spans="1:16" ht="18" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="E90" s="1"/>
       <c r="F90" s="45">
         <f>F3</f>
@@ -4585,7 +4587,7 @@
       </c>
       <c r="K90" s="54">
         <f t="shared" si="0"/>
-        <v>508</v>
+        <v>583</v>
       </c>
       <c r="L90" s="54">
         <f t="shared" si="0"/>
@@ -5676,6 +5678,41 @@
     </row>
   </sheetData>
   <mergeCells count="51">
+    <mergeCell ref="C83:C85"/>
+    <mergeCell ref="D81:D82"/>
+    <mergeCell ref="D83:D87"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="D77:D79"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="C72:C73"/>
+    <mergeCell ref="D72:D73"/>
+    <mergeCell ref="A70:A71"/>
+    <mergeCell ref="C61:C62"/>
+    <mergeCell ref="D61:D62"/>
+    <mergeCell ref="C70:C71"/>
+    <mergeCell ref="D70:D71"/>
+    <mergeCell ref="A61:A62"/>
+    <mergeCell ref="A63:A66"/>
+    <mergeCell ref="C63:C66"/>
+    <mergeCell ref="D63:D66"/>
+    <mergeCell ref="C52:C55"/>
+    <mergeCell ref="D52:D55"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="C10:C16"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="C38:C44"/>
+    <mergeCell ref="D38:D45"/>
+    <mergeCell ref="D18:D19"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="A32:M32"/>
+    <mergeCell ref="A38:A44"/>
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="A50:A51"/>
+    <mergeCell ref="A52:A55"/>
+    <mergeCell ref="C48:C49"/>
+    <mergeCell ref="C50:C51"/>
     <mergeCell ref="A59:M59"/>
     <mergeCell ref="A76:M76"/>
     <mergeCell ref="A2:A3"/>
@@ -5692,41 +5729,6 @@
     <mergeCell ref="C2:C3"/>
     <mergeCell ref="D50:D51"/>
     <mergeCell ref="D48:D49"/>
-    <mergeCell ref="C52:C55"/>
-    <mergeCell ref="D52:D55"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="C10:C16"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="C38:C44"/>
-    <mergeCell ref="D38:D45"/>
-    <mergeCell ref="D18:D19"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="A32:M32"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="C72:C73"/>
-    <mergeCell ref="D72:D73"/>
-    <mergeCell ref="A70:A71"/>
-    <mergeCell ref="C61:C62"/>
-    <mergeCell ref="D61:D62"/>
-    <mergeCell ref="C70:C71"/>
-    <mergeCell ref="D70:D71"/>
-    <mergeCell ref="A61:A62"/>
-    <mergeCell ref="A63:A66"/>
-    <mergeCell ref="C63:C66"/>
-    <mergeCell ref="D63:D66"/>
-    <mergeCell ref="A38:A44"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="A52:A55"/>
-    <mergeCell ref="C48:C49"/>
-    <mergeCell ref="C50:C51"/>
-    <mergeCell ref="C83:C85"/>
-    <mergeCell ref="D81:D82"/>
-    <mergeCell ref="D83:D87"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="D77:D79"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="0" copies="0" r:id="rId1"/>
